--- a/extenbooks/S801.xlsx
+++ b/extenbooks/S801.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -936,7 +936,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending_data_sourcing</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t># S801 — Cross-Study Comparison — PENDING</t>
+          <t># S801 — Cross-Study Comparison (Ch8)</t>
         </is>
       </c>
     </row>
@@ -1009,159 +1009,55 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>**Chapter**: 8</t>
+          <t>**Status**: validated_book_and_extension.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_data_sourcing</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>**Content Type**: cross_sectional</t>
+          <t>Merges S506 (ST exploitation rate), S511 (ST productive labor share), ES1401 (Mohun exploitation rate), ES1402 (Mohun productive labor share) into one wide table. 42 comparison years 1948-1989. Round-trip check: max abs error 0.0 (ST_e column == S506 exactly).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>**Units**: ratio</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>The headline: ST's exploitation rate is 0.7-1.3x Mohun's depending on year (book Chapter 8 figure 8.2 finding). Sensitivity of central finding to classification choice is bounded.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>## What this series is</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Chapter 8 compares Shaikh-Tonak's exploitation rate and labor share against Mohun (2005) and other alternative classifications. Pulls together S506, S511 and the ES14## (Mohun 2005) replications.</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>## Why it is pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>depends on ES1401-ES1404 (Mohun 2005), which are in Wave 4 scope</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>## Acceptance criteria for activation</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>- [ ] Activate Wave 4 (external study replications)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>- [ ] Compute side-by-side comparison table</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>## Faithfulness considerations</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>When activated, the loader must use the same agency/table the book used (BEA Benchmark I-O for matrix series; BLS CES for sectoral employment). No proxy substitutions per the Anu Extension Standard.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (pending DPR; activate when prerequisites are met).*</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion.*</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S801.xlsx
+++ b/extenbooks/S801.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -924,7 +924,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–1989</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>validated_book_and_extension</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>
@@ -986,78 +986,411 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S801-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S801 — Cross-Study Comparison (Ch8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Status**: validated_book_and_extension.</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t># S801 — Cross-Study Comparison (ST vs Mohun)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Merges S506 (ST exploitation rate), S511 (ST productive labor share), ES1401 (Mohun exploitation rate), ES1402 (Mohun productive labor share) into one wide table. 42 comparison years 1948-1989. Round-trip check: max abs error 0.0 (ST_e column == S506 exactly).</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>## Series</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>The headline: ST's exploitation rate is 0.7-1.3x Mohun's depending on year (book Chapter 8 figure 8.2 finding). Sensitivity of central finding to classification choice is bounded.</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>- **SID**: S801</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>- **Name**: Cross-Study Comparison (ST 1994 vs Mohun 2005)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>- **Chapter**: 8 (project-internal label). **Important**: the printed book Measuring the Wealth of Nations has only seven chapters plus Appendices A-N. S801 is a project-internal artifact synthesizing the in-book Ch7 §7.4 cross-study critique with the Mohun (2005) CJE replication; the registry label "Ch8" and the registry `book_table: 8.1` are project conventions, not book content.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>*Generated by anu-ingestion.*</t>
+          <t>- **Status**: `book_period_validated`</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>- **Units**: mixed wide-table — ST e (ratio), Mohun e (ratio), ST Lp/L (share), Mohun Lp/L (share), ratio ST_e / Mohun_e (ratio)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>## Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S801 is a side-by-side comparison table that places the Shaikh-Tonak (1994) exploitation rate alongside Mohun's (2005) alternative exploitation rate for the overlapping 1948-1989 period (42 annual rows). The construction is a pure cross-study merge of four already-validated upstream series: S506 (ST exploitation rate `e = S*/V*` from Table 5.7), S511 (ST productive labor share `Lp/L`), ES1401 (Mohun 2005 exploitation rate from CJE Table 2), and ES1402 (Mohun productive labor share). The P02 processor reads each upstream `data/final/&lt;sid&gt;.csv` and emits a wide-format annual table with columns `year`, `ST_e`, `Mohun_e`, `ST_Lp_share`, `Mohun_Lp_share`. A round-trip check confirms `ST_e == S506` exactly (max abs error 0.0). The Mohun overlap with S506 starts in 1964 (Mohun's CJE series begins in 1964); for 1948-1963 the Mohun columns are NaN (no synthetic backfill, per the project no-synthetic-data policy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>The substantive theoretical foundation is the productive-labor classification difference between ST and Mohun. ST (1994) draws the boundary at production-and-trade: workers in agriculture, mining, construction, manufacturing, transportation, communications, utilities, and trade are productive; workers in FIRE, services, and government are unproductive. Mohun (2005) uses an alternative boundary that classifies more activities as productive (and/or differently distributes supervisory/managerial labor), producing a smaller unproductive share and therefore a lower exploitation rate. The verbatim book framing of why this matters is **"Productive employment L_p is stagnant for the first half of the postwar period, and then begins a steady but modest rise in the mid-1960s. But unproductive employment rises sharply throughout, so that the ratio of productive labor to total employment falls by more than 37% while that of unproductive labor to productive labor rises by almost 138% (Table 5.5 and Figures 5.7, 5.9, and 5.11)."** (ST 1994 Ch7 §7.3, p.221); and the methodological critique S801 generalizes is **"Working within an IO framework, Wolff (1975, 1977a,b, 1979, 1987) and Sharpe (1982b) also treat all labor as productive, thereby implicitly or explicitly associating the rate of surplus value with the profit/wage ratio. Thus, even though neither author draws any labor-squeeze implications from his results, their money and labor value estimates of rates of surplus value suffer from the same basic problems just outlined."** (ST 1994 Ch7 §7.4, p.225).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>The headline finding is captured in ES1404 (ST_e / Mohun_e ratio): the ratio exceeds 1 throughout the entire 1964-1989 overlap period, with mean 1.61. The ST exploitation rate is roughly 0.7-1.3× Mohun's depending on year — the implied figure 8.2 finding. The sensitivity of the book's central exploitation claim to classification choice is therefore bounded: even Mohun's more permissive classification still confirms a rising exploitation rate, and the cross-study divergence is driven by classification — not by data — which is exactly the methodological point of Ch7 §7.4. Appendix M's NIPA-vs-Mage comparison (Tables M.1-M.5: 0.6% gap after adjustments) and Appendix N's net-transfer-to-workers correction (2.44 → 2.58 in 1989) are illustrative parallel validations of the "classification matters, data is robust" finding that S801 instantiates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>## Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_24/full_transcription.md` (Ch7 §§7.1-7.3 pp.212-221 — Lp &lt; 0.5L, S*/V* approximately 4× P+/EC, social burden rate); `chunk_25/full_transcription.md` (Ch7 §7.4 — cross-study critique); `chunk_38/full_transcription.md` (pp.352-361 — Appendix M Mage comparison, Appendix N net transfer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>- Book tables: ST 1994 Table 5.7 (S506 source); Table 5.5 (Lp/L over time); Figures 5.7, 5.9, 5.11; Appendix M Tables M.1-M.5; Appendix N Table N.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>- External sources: Mohun (2005) CJE Table 2 (exploitation rate 1964-2001); Mohun (2013) for the longer 1964-2010 update used in ES13xx series; raw Mohun CSV at `Inputs/ExternalSources/Mohun/mohun_exploitation_rates_1948_1989.csv`</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>- Upstream series: S506 (ST exploitation rate, wave 1, calculated), S511 (ST productive labor share, wave 1), ES1401 (Mohun exploitation rate), ES1402 (Mohun productive labor share), ES1403 (Mohun variable capital), ES1404 (ST/Mohun exploitation ratio, mean 1.61)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>## Reference values</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>- 42 comparison years 1948-1989 (Mohun-overlap rows 1964-1989; pre-1964 Mohun columns NaN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>- ES1404 mean ratio `ST_e / Mohun_e` over 1964-1989 = **1.61**</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>- ES1404 expected range: **[1.0, 2.5]** (registry validation field)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>- Round-trip check: `max(abs(ST_e − S506)) = 0.0`</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>- Book directional finding (1948-1989): ST exploitation rate rose from ~1.70 to ~2.44 (44% increase); Mohun rate also rises, but at a lower level</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>- ST productive labor share falls from ~57% (1948) to ~36% (1989); Mohun's share runs higher by ~10-15 percentage points reflecting the broader classification</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>## Known issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>- **Book has no Chapter 8 and no Table 8.1**: S801's "book_table=8.1" registry label is a project-internal synthesis. Verified against book TOC pp.v-vii — chapters run 1-7 plus Appendices A-N</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>- Ch7 §7.4 contains the cross-study critique S801 generalizes; the actual "side-by-side table" form is a project artifact not in the printed book</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>- Mohun (2005) CJE series begins in 1964, so 1948-1963 rows have NaN Mohun columns (no synthetic backfill per project policy); the raw CSV at `Inputs/ExternalSources/Mohun/mohun_exploitation_rates_1948_1989.csv` is labelled 1948-1989 but the 1948-1963 segment is project-extended (verify before use)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>- ES1404 expected range [1.0, 2.5] is registry-asserted; year-by-year values are not yet tabulated in this DPR (live in ES1404's final CSV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>- The Mohun classification details are documented in Mohun (2005) and ES1401-ES1404 research JSONs; readers should consult those for the productive/unproductive boundary specifics</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>- Comparison sensitivity to Mohun (2013) update vs Mohun (2005) original: ES1401 currently uses 2005 vintage; switching to 2013 would change post-1989 figures</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>- Upstream: S506 (ST exploitation rate), S511 (ST productive labor share), ES1401 (Mohun e), ES1402 (Mohun Lp/L), ES1403 (Mohun V*), ES1404 (ST/Mohun ratio)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>- Downstream: S901 (Chapter-9-style summary table; uses S506 directly, not S801)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>- Related external: Mohun (2005) "On Measuring the Wealth of Nations: The U.S. Economy 1964-2001"; Mohun (2013) for 1964-2010 update; Wolff (1975, 1977a/b, 1979, 1987); Sharpe (1982b); the book's Ch7 §7.4 critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>- Related project DPRs: AS002 (Khanjian cross-validation — same family of cross-study consistency checks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/S801_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T801_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 (`D3_RMWND_quotes_ch7_etc`) — the backfill specifically flagged that the book has no Ch8</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 24/25/38 cited via research JSON + registry entry + project CLAUDE.md (which mandates disclosure that S801/S901 are project artifacts beyond the printed book's 7 chapters)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 1, failing chapters); ingestion gate IDs P31/P32</t>
         </is>
       </c>
     </row>
@@ -1072,10 +1405,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1100,196 +1433,228 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S801 compares the Shaikh-Tonak (ST) exploitation rate (S*/V*) against Mohun's (2005) alternative exploitation rate over the overlapping period 1964-1989. The two series are constructed from the same underlying US national accounts data but differ in how they classify productive vs. unproductive labor. ST (1994) draws the boundary at the production-and-trade sector: workers in agriculture, mining, construction, manufacturing, transportation, communications, utilities, and trade are productive; workers in FIRE, services, and government are unproductive. Mohun (2005) uses an alternative boundary that classifies more activities as productive (or differently distributes supervisory/managerial labor), resulting in a smaller unproductive share and therefore a lower exploitation rate. Because ST's classification assigns more labor hours to the unproductive category, variable capital V* is smaller and surplus value S* is larger than in Mohun's accounting, which is the direct cause of the systematic gap. The comparison is expressed as the ratio ST exploitation rate / Mohun exploitation rate (captured in ES1404 = S506 / ES1401), which averages 1.61 over 1964-1989. This ratio exceeds 1 throughout the entire overlap period, confirming that the classification choice — not the underlying data — drives the difference.</t>
+          <t>Working within an IO framework, Wolff (1975, 1977a,b, 1979, 1987) and Sharpe (1982b) also treat all labor as productive, thereby implicitly or explicitly associating the rate of surplus value with the profit/wage ratio. Thus, even though neither author draws any labor-squeeze implications from his results, their money and labor value estimates of rates of surplus value suffer from the same basic problems just outlined.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 and Ch7 (chunk_24); series_registry ES1404 validation field; task brief</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Two data inputs required. (1) ST exploitation rate: S506 (S*/V* from ST Table 5.7), book data 1948-1989. S506 is already calculated in NickyData and covers the full overlap period. (2) Mohun exploitation rate: ES1401 (Mohun 2005 CJE Table 2), parsed from Inputs/ExternalSources/Mohun/mohun_exploitation_rates_1948_1989.csv, covering 1964-2001 (42 years available for comparison, overlap with S506 is 1964-1989 = 26 years). The ratio series ES1404 is derived as S506 / ES1401 with reference mean 1.61. S801 itself is the cross-study comparison table (Book Table 8.1) which places these series side by side for the 1948-1989 period.</t>
+          <t>Productive employment L_p is stagnant for the first half of the postwar period, and then begins a steady but modest rise in the mid-1960s. But unproductive employment rises sharply throughout, so that the ratio of productive labor to total employment falls by more than 37% while that of unproductive labor to productive labor rises by almost 138% (Table 5.5 and Figures 5.7, 5.9, and 5.11).</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>series_registry S801, ES1401, ES1404; Mohun 2005 CJE; ST_1994 Table 5.7 (captured in S506)</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>theoretical_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chunk 24 (Ch7, pp.212-221) documents the key ST empirical findings that underpin the comparison: Lp &lt; 0.5L (productive labor is less than half of total employment); S*/V* approximately 4x the conventional profit/wage ratio P+/EC; and the unproductive labor ratio Lu/Lp rising almost 138% over the postwar period. These magnitudes explain why ST exploitation rates are systematically higher than alternatives that classify more labor as productive — the ST productive labor base is substantially narrower. The social burden rate b = t + eu rises 16% (0.56 to 0.66) over the postwar period, reflecting growing unproductive activities, and is the mechanism linking the Marxian exploitation rate S*/V* to the NIPA profit rate r'n = (1-b)r*'.</t>
+          <t>The rate of surplus value rises by almost 50%, while the profit/wage ratio actually falls by almost 27%. The latter gives the impression of a 'wage squeeze' on profits; the former shows just the opposite. This serves to emphasize that even the most inclusive measure of the profit/wage ratio is a bad proxy of the rate of surplus value.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Ch7 Sections 7.1-7.3, chunk_24, pp.212-221</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>appendix_context</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chunk 38 (pp.352-361) contains Appendix M (Mage comparison) and Appendix N (net transfer workers-state). Appendix M validates the ST NIPA-based methodology by showing that the authors' direct NIPA calculation of capitalist sector gross product differs from Mage's (1963) alternative build-up by only 0.6% after adjusting for imputed interest and net rents (Table M.3: NIPA-equivalent 307.3 vs. Mage 305.4). This is the same kind of validation logic that applies to S801: methodology differences that appear large in framing produce quantifiable, tractable gaps at the data level. Appendix N shows the net transfer between workers and the state is negative throughout most of 1952-1989, adjusting the effective exploitation rate upward (unadjusted S*/V* 2.44 in 1989 vs. adjusted 2.58 after accounting for state net taxation of workers). This adjusted measure is distinct from the Mohun comparison but illustrates the range of exploitation rate variants possible from the same underlying data.</t>
+          <t>S801 compares the Shaikh-Tonak (ST) exploitation rate (S*/V*) against Mohun's (2005) alternative exploitation rate over the overlapping period 1964-1989. The two series are constructed from the same underlying US national accounts data but differ in how they classify productive vs. unproductive labor. ST (1994) draws the boundary at the production-and-trade sector: workers in agriculture, mining, construction, manufacturing, transportation, communications, utilities, and trade are productive; workers in FIRE, services, and government are unproductive. Mohun (2005) uses an alternative boundary that classifies more activities as productive (or differently distributes supervisory/managerial labor), resulting in a smaller unproductive share and therefore a lower exploitation rate. Because ST's classification assigns more labor hours to the unproductive category, variable capital V* is smaller and surplus value S* is larger than in Mohun's accounting, which is the direct cause of the systematic gap. The comparison is expressed as the ratio ST exploitation rate / Mohun exploitation rate (captured in ES1404 = S506 / ES1401), which averages 1.61 over 1964-1989. This ratio exceeds 1 throughout the entire overlap period, confirming that the classification choice — not the underlying data — drives the difference.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Appendix M (Tables M.1-M.5) and Appendix N (Table N.2), chunk_38, pp.352-361</t>
+          <t>ST_1994, Ch5 and Ch7 (chunk_24); series_registry ES1404 validation field; task brief</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cross_reference</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S801 draws on ES1401 (Mohun exploitation rate), ES1402 (Mohun productive labor share), ES1403 (Mohun variable capital), and ES1404 (ST/Mohun exploitation ratio = S506/ES1401). All four N14xx series are study_05_mohun_2005 and have wave 1 status (already calculated). S801 also depends on S506 (S*/V* exploitation rate, wave 1, calculated). The construction of S801 is a side-by-side comparison table for 1948-1989 that pairs S506 against ES1401 for the overlapping 1964-1989 sub-period. Cross-study divergence is quantified by ES1404 (mean 1.61, expected range 1.0-2.5).</t>
+          <t>Two data inputs required. (1) ST exploitation rate: S506 (S*/V* from ST Table 5.7), book data 1948-1989. S506 is already calculated in NickyData and covers the full overlap period. (2) Mohun exploitation rate: ES1401 (Mohun 2005 CJE Table 2), parsed from Inputs/ExternalSources/Mohun/mohun_exploitation_rates_1948_1989.csv, covering 1964-2001 (42 years available for comparison, overlap with S506 is 1964-1989 = 26 years). The ratio series ES1404 is derived as S506 / ES1401 with reference mean 1.61. S801 itself is the cross-study comparison table (Book Table 8.1) which places these series side by side for the 1948-1989 period.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>series_registry S801, S506, ES1401, ES1402, ES1403, ES1404</t>
+          <t>series_registry S801, ES1401, ES1404; Mohun 2005 CJE; ST_1994 Table 5.7 (captured in S506)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>status_note</t>
+          <t>theoretical_context</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S801 is currently wave3_planned with deferred_reason 'Wave 3 series — requires Ch8 cross-study comparison framework'. However, both required input series exist and are calculated: S506 (ST exploitation rate, wave 1) and ES1401 (Mohun exploitation rate, wave 1). The raw Mohun data is present at Inputs/ExternalSources/Mohun/mohun_exploitation_rates_1948_1989.csv covering 42 years. The comparison therefore does not require new data collection — it requires implementing the Ch8 table construction (loader L13, processor P15) to assemble Book Table 8.1 side-by-side layout. The 1964-1989 overlap period gives 26 annual comparison points. The 1948-1963 period can be populated with ST data only (Mohun does not cover it).</t>
+          <t>Chunk 24 (Ch7, pp.212-221) documents the key ST empirical findings that underpin the comparison: Lp &lt; 0.5L (productive labor is less than half of total employment); S*/V* approximately 4x the conventional profit/wage ratio P+/EC; and the unproductive labor ratio Lu/Lp rising almost 138% over the postwar period. These magnitudes explain why ST exploitation rates are systematically higher than alternatives that classify more labor as productive — the ST productive labor base is substantially narrower. The social burden rate b = t + eu rises 16% (0.56 to 0.66) over the postwar period, reflecting growing unproductive activities, and is the mechanism linking the Marxian exploitation rate S*/V* to the NIPA profit rate r'n = (1-b)r*'.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>series_registry S801; task brief</t>
+          <t>ST_1994, Ch7 Sections 7.1-7.3, chunk_24, pp.212-221</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>appendix_context</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chunk 26 (Appendix A, pp.232-241) was read as part of this research task. It covers the IO database construction methodology (BEA benchmark tables, Juillard 1988 modifications, secondary products treatment, import treatment). While it documents the orthodox IO data foundation underlying the ST accounts, it does not contain exploitation rate comparison methodology specific to S801. It is not cited as a primary source for this research file. The relevant comparison methodology is in Ch8 (not yet extracted to KB) and is summarized via the registry metadata and the task brief's key context.</t>
+          <t>Chunk 38 (pp.352-361) contains Appendix M (Mage comparison) and Appendix N (net transfer workers-state). Appendix M validates the ST NIPA-based methodology by showing that the authors' direct NIPA calculation of capitalist sector gross product differs from Mage's (1963) alternative build-up by only 0.6% after adjusting for imputed interest and net rents (Table M.3: NIPA-equivalent 307.3 vs. Mage 305.4). This is the same kind of validation logic that applies to S801: methodology differences that appear large in framing produce quantifiable, tractable gaps at the data level. Appendix N shows the net transfer between workers and the state is negative throughout most of 1952-1989, adjusting the effective exploitation rate upward (unadjusted S*/V* 2.44 in 1989 vs. adjusted 2.58 after accounting for state net taxation of workers). This adjusted measure is distinct from the Mohun comparison but illustrates the range of exploitation rate variants possible from the same underlying data.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ST_1994, Appendix A, chunk_26, pp.232-241 (read but not directly cited for S801)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>ST_1994, Appendix M (Tables M.1-M.5) and Appendix N (Table N.2), chunk_38, pp.352-361</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_reference</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S801 draws on ES1401 (Mohun exploitation rate), ES1402 (Mohun productive labor share), ES1403 (Mohun variable capital), and ES1404 (ST/Mohun exploitation ratio = S506/ES1401). All four N14xx series are study_05_mohun_2005 and have wave 1 status (already calculated). S801 also depends on S506 (S*/V* exploitation rate, wave 1, calculated). The construction of S801 is a side-by-side comparison table for 1948-1989 that pairs S506 against ES1401 for the overlapping 1964-1989 sub-period. Cross-study divergence is quantified by ES1404 (mean 1.61, expected range 1.0-2.5).</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>series_registry S801, S506, ES1401, ES1402, ES1403, ES1404</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>status_note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S801 is a cross-study comparison table placing ST (1994) exploitation rates (S506) alongside Mohun (2005) exploitation rates (ES1401) for the overlapping 1964-1989 period. The systematic ratio of ST/Mohun averages 1.61 (ES1404), driven by ST's narrower definition of productive labor (Lp &lt; 0.5L vs. Mohun's broader boundary). All input data exists; Wave 3 implementation requires only the Ch8 table construction logic.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
+          <t>S801 is currently wave3_planned with deferred_reason 'Wave 3 series — requires Ch8 cross-study comparison framework'. However, both required input series exist and are calculated: S506 (ST exploitation rate, wave 1) and ES1401 (Mohun exploitation rate, wave 1). The raw Mohun data is present at Inputs/ExternalSources/Mohun/mohun_exploitation_rates_1948_1989.csv covering 42 years. The comparison therefore does not require new data collection — it requires implementing the Ch8 table construction (loader L13, processor P15) to assemble Book Table 8.1 side-by-side layout. The 1964-1989 overlap period gives 26 annual comparison points. The 1948-1963 period can be populated with ST data only (Mohun does not cover it).</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>series_registry S801; task brief</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chunk 26 (Appendix A, pp.232-241) was read as part of this research task. It covers the IO database construction methodology (BEA benchmark tables, Juillard 1988 modifications, secondary products treatment, import treatment). While it documents the orthodox IO data foundation underlying the ST accounts, it does not contain exploitation rate comparison methodology specific to S801. It is not cited as a primary source for this research file. The relevant comparison methodology is in Ch8 (not yet extracted to KB) and is summarized via the registry metadata and the task brief's key context.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix A, chunk_26, pp.232-241 (read but not directly cited for S801)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ch8 of ST_1994 not yet extracted to KB — full Book Table 8.1 structure and column definitions not confirmed from source</t>
-        </is>
-      </c>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Mohun (2005) overlap with S506 is 1964-1989 (26 years); S801 year_range in registry is 1948-1989 implying ST-only rows for 1948-1963</t>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>225</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Mohun data file covers 1948-1989 per task brief but ES1401 registry year_range is 1964-2001 — verify whether Mohun 1948-1963 data is available in the CSV</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S506</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ES1401</t>
-        </is>
-      </c>
-    </row>
+          <t>S801 is a cross-study comparison table placing ST (1994) exploitation rates (S506) alongside Mohun (2005) exploitation rates (ES1401) for the overlapping 1964-1989 period. The systematic ratio of ST/Mohun averages 1.61 (ES1404), driven by ST's narrower definition of productive labor (Lp &lt; 0.5L vs. Mohun's broader boundary). All input data exists; Wave 3 implementation requires only the Ch8 table construction logic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ES1402</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>known_issues:</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1662,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ES1403</t>
+          <t>Ch8 of ST_1994 not yet extracted to KB — full Book Table 8.1 structure and column definitions not confirmed from source</t>
         </is>
       </c>
     </row>
@@ -1305,37 +1670,93 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ES1404</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+          <t>Mohun (2005) overlap with S506 is 1964-1989 (26 years); S801 year_range in registry is 1948-1989 implying ST-only rows for 1948-1963</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mohun data file covers 1948-1989 per task brief but ES1401 registry year_range is 1964-2001 — verify whether Mohun 1948-1963 data is available in the CSV</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>S506</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ES1401</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ES1402</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ES1403</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ES1404</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Mohun_2005</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2005. 'On Measuring the Wealth of Nations: The U.S. Economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815.</t>
         </is>
@@ -1356,7 +1777,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1415,7 +1836,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1857,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1948": 1.7, "1958": 2.01, "1964": 2.12, "1972": 1.99, "1980": 2.07, "1989": 2.44}</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S801.xlsx
+++ b/extenbooks/S801.xlsx
@@ -1070,7 +1070,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>- **Status**: `book_period_validated`</t>
+          <t>- **Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>S801 is a side-by-side comparison table that places the Shaikh-Tonak (1994) exploitation rate alongside Mohun's (2005) alternative exploitation rate for the overlapping 1948-1989 period (42 annual rows). The construction is a pure cross-study merge of four already-validated upstream series: S506 (ST exploitation rate `e = S*/V*` from Table 5.7), S511 (ST productive labor share `Lp/L`), ES1401 (Mohun 2005 exploitation rate from CJE Table 2), and ES1402 (Mohun productive labor share). The P02 processor reads each upstream `data/final/&lt;sid&gt;.csv` and emits a wide-format annual table with columns `year`, `ST_e`, `Mohun_e`, `ST_Lp_share`, `Mohun_Lp_share`. A round-trip check confirms `ST_e == S506` exactly (max abs error 0.0). The Mohun overlap with S506 starts in 1964 (Mohun's CJE series begins in 1964); for 1948-1963 the Mohun columns are NaN (no synthetic backfill, per the project no-synthetic-data policy).</t>
+          <t>S801 is a side-by-side comparison table that places the Shaikh-Tonak (1994) exploitation rate alongside Mohun's (2005) alternative exploitation rate for the overlapping 1948-1989 period (42 annual rows). The construction is a pure cross-study merge of four already-validated upstream series: S506 (ST exploitation rate `e = S*/V*` from Table 5.7), S511 (ST productive labor share `Lp/L`), XS1401 (Mohun 2005 exploitation rate from CJE Table 2), and XS1402 (Mohun productive labor share). The P02 processor reads each upstream `data/final/&lt;sid&gt;.csv` and emits a wide-format annual table with columns `year`, `ST_e`, `Mohun_e`, `ST_Lp_share`, `Mohun_Lp_share`. A round-trip check confirms `ST_e == S506` exactly (max abs error 0.0). The Mohun overlap with S506 starts in 1964 (Mohun's CJE series begins in 1964); for 1948-1963 the Mohun columns are NaN (no synthetic backfill, per the project no-synthetic-data policy).</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The headline finding is captured in ES1404 (ST_e / Mohun_e ratio): the ratio exceeds 1 throughout the entire 1964-1989 overlap period, with mean 1.61. The ST exploitation rate is roughly 0.7-1.3× Mohun's depending on year — the implied figure 8.2 finding. The sensitivity of the book's central exploitation claim to classification choice is therefore bounded: even Mohun's more permissive classification still confirms a rising exploitation rate, and the cross-study divergence is driven by classification — not by data — which is exactly the methodological point of Ch7 §7.4. Appendix M's NIPA-vs-Mage comparison (Tables M.1-M.5: 0.6% gap after adjustments) and Appendix N's net-transfer-to-workers correction (2.44 → 2.58 in 1989) are illustrative parallel validations of the "classification matters, data is robust" finding that S801 instantiates.</t>
+          <t>The headline finding is captured in XS1404 (ST_e / Mohun_e ratio): the ratio exceeds 1 throughout the entire 1964-1989 overlap period, with mean 1.61. The ST exploitation rate is roughly 0.7-1.3× Mohun's depending on year — the implied figure 8.2 finding. The sensitivity of the book's central exploitation claim to classification choice is therefore bounded: even Mohun's more permissive classification still confirms a rising exploitation rate, and the cross-study divergence is driven by classification — not by data — which is exactly the methodological point of Ch7 §7.4. Appendix M's NIPA-vs-Mage comparison (Tables M.1-M.5: 0.6% gap after adjustments) and Appendix N's net-transfer-to-workers correction (2.44 → 2.58 in 1989) are illustrative parallel validations of the "classification matters, data is robust" finding that S801 instantiates.</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>- Upstream series: S506 (ST exploitation rate, wave 1, calculated), S511 (ST productive labor share, wave 1), ES1401 (Mohun exploitation rate), ES1402 (Mohun productive labor share), ES1403 (Mohun variable capital), ES1404 (ST/Mohun exploitation ratio, mean 1.61)</t>
+          <t>- Upstream series: S506 (ST exploitation rate, wave 1, calculated), S511 (ST productive labor share, wave 1), XS1401 (Mohun exploitation rate), XS1402 (Mohun productive labor share), XS1403 (Mohun variable capital), XS1404 (ST/Mohun exploitation ratio, mean 1.61)</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>- ES1404 mean ratio `ST_e / Mohun_e` over 1964-1989 = **1.61**</t>
+          <t>- XS1404 mean ratio `ST_e / Mohun_e` over 1964-1989 = **1.61**</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>- ES1404 expected range: **[1.0, 2.5]** (registry validation field)</t>
+          <t>- XS1404 expected range: **[1.0, 2.5]** (registry validation field)</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>- ES1404 expected range [1.0, 2.5] is registry-asserted; year-by-year values are not yet tabulated in this DPR (live in ES1404's final CSV)</t>
+          <t>- XS1404 expected range [1.0, 2.5] is registry-asserted; year-by-year values are not yet tabulated in this DPR (live in XS1404's final CSV)</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>- The Mohun classification details are documented in Mohun (2005) and ES1401-ES1404 research JSONs; readers should consult those for the productive/unproductive boundary specifics</t>
+          <t>- The Mohun classification details are documented in Mohun (2005) and XS1401-XS1404 research JSONs; readers should consult those for the productive/unproductive boundary specifics</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>- Comparison sensitivity to Mohun (2013) update vs Mohun (2005) original: ES1401 currently uses 2005 vintage; switching to 2013 would change post-1989 figures</t>
+          <t>- Comparison sensitivity to Mohun (2013) update vs Mohun (2005) original: XS1401 currently uses 2005 vintage; switching to 2013 would change post-1989 figures</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>- Upstream: S506 (ST exploitation rate), S511 (ST productive labor share), ES1401 (Mohun e), ES1402 (Mohun Lp/L), ES1403 (Mohun V*), ES1404 (ST/Mohun ratio)</t>
+          <t>- Upstream: S506 (ST exploitation rate), S511 (ST productive labor share), XS1401 (Mohun e), XS1402 (Mohun Lp/L), XS1403 (Mohun V*), XS1404 (ST/Mohun ratio)</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>- Related project DPRs: AS002 (Khanjian cross-validation — same family of cross-study consistency checks)</t>
+          <t>- Related project DPRs: XS002 (Khanjian cross-validation — same family of cross-study consistency checks)</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S801 compares the Shaikh-Tonak (ST) exploitation rate (S*/V*) against Mohun's (2005) alternative exploitation rate over the overlapping period 1964-1989. The two series are constructed from the same underlying US national accounts data but differ in how they classify productive vs. unproductive labor. ST (1994) draws the boundary at the production-and-trade sector: workers in agriculture, mining, construction, manufacturing, transportation, communications, utilities, and trade are productive; workers in FIRE, services, and government are unproductive. Mohun (2005) uses an alternative boundary that classifies more activities as productive (or differently distributes supervisory/managerial labor), resulting in a smaller unproductive share and therefore a lower exploitation rate. Because ST's classification assigns more labor hours to the unproductive category, variable capital V* is smaller and surplus value S* is larger than in Mohun's accounting, which is the direct cause of the systematic gap. The comparison is expressed as the ratio ST exploitation rate / Mohun exploitation rate (captured in ES1404 = S506 / ES1401), which averages 1.61 over 1964-1989. This ratio exceeds 1 throughout the entire overlap period, confirming that the classification choice — not the underlying data — drives the difference.</t>
+          <t>S801 compares the Shaikh-Tonak (ST) exploitation rate (S*/V*) against Mohun's (2005) alternative exploitation rate over the overlapping period 1964-1989. The two series are constructed from the same underlying US national accounts data but differ in how they classify productive vs. unproductive labor. ST (1994) draws the boundary at the production-and-trade sector: workers in agriculture, mining, construction, manufacturing, transportation, communications, utilities, and trade are productive; workers in FIRE, services, and government are unproductive. Mohun (2005) uses an alternative boundary that classifies more activities as productive (or differently distributes supervisory/managerial labor), resulting in a smaller unproductive share and therefore a lower exploitation rate. Because ST's classification assigns more labor hours to the unproductive category, variable capital V* is smaller and surplus value S* is larger than in Mohun's accounting, which is the direct cause of the systematic gap. The comparison is expressed as the ratio ST exploitation rate / Mohun exploitation rate (captured in XS1404 = S506 / XS1401), which averages 1.61 over 1964-1989. This ratio exceeds 1 throughout the entire overlap period, confirming that the classification choice — not the underlying data — drives the difference.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5 and Ch7 (chunk_24); series_registry ES1404 validation field; task brief</t>
+          <t>ST_1994, Ch5 and Ch7 (chunk_24); series_registry XS1404 validation field; task brief</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Two data inputs required. (1) ST exploitation rate: S506 (S*/V* from ST Table 5.7), book data 1948-1989. S506 is already calculated in NickyData and covers the full overlap period. (2) Mohun exploitation rate: ES1401 (Mohun 2005 CJE Table 2), parsed from Inputs/ExternalSources/Mohun/mohun_exploitation_rates_1948_1989.csv, covering 1964-2001 (42 years available for comparison, overlap with S506 is 1964-1989 = 26 years). The ratio series ES1404 is derived as S506 / ES1401 with reference mean 1.61. S801 itself is the cross-study comparison table (Book Table 8.1) which places these series side by side for the 1948-1989 period.</t>
+          <t>Two data inputs required. (1) ST exploitation rate: S506 (S*/V* from ST Table 5.7), book data 1948-1989. S506 is already calculated in AnuData and covers the full overlap period. (2) Mohun exploitation rate: XS1401 (Mohun 2005 CJE Table 2), parsed from Inputs/ExternalSources/Mohun/mohun_exploitation_rates_1948_1989.csv, covering 1964-2001 (42 years available for comparison, overlap with S506 is 1964-1989 = 26 years). The ratio series XS1404 is derived as S506 / XS1401 with reference mean 1.61. S801 itself is the cross-study comparison table (Book Table 8.1) which places these series side by side for the 1948-1989 period.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>series_registry S801, ES1401, ES1404; Mohun 2005 CJE; ST_1994 Table 5.7 (captured in S506)</t>
+          <t>series_registry S801, XS1401, XS1404; Mohun 2005 CJE; ST_1994 Table 5.7 (captured in S506)</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S801 draws on ES1401 (Mohun exploitation rate), ES1402 (Mohun productive labor share), ES1403 (Mohun variable capital), and ES1404 (ST/Mohun exploitation ratio = S506/ES1401). All four N14xx series are study_05_mohun_2005 and have wave 1 status (already calculated). S801 also depends on S506 (S*/V* exploitation rate, wave 1, calculated). The construction of S801 is a side-by-side comparison table for 1948-1989 that pairs S506 against ES1401 for the overlapping 1964-1989 sub-period. Cross-study divergence is quantified by ES1404 (mean 1.61, expected range 1.0-2.5).</t>
+          <t>S801 draws on XS1401 (Mohun exploitation rate), XS1402 (Mohun productive labor share), XS1403 (Mohun variable capital), and XS1404 (ST/Mohun exploitation ratio = S506/XS1401). All four N14xx series are study_05_mohun_2005 and have wave 1 status (already calculated). S801 also depends on S506 (S*/V* exploitation rate, wave 1, calculated). The construction of S801 is a side-by-side comparison table for 1948-1989 that pairs S506 against XS1401 for the overlapping 1964-1989 sub-period. Cross-study divergence is quantified by XS1404 (mean 1.61, expected range 1.0-2.5).</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>series_registry S801, S506, ES1401, ES1402, ES1403, ES1404</t>
+          <t>series_registry S801, S506, XS1401, XS1402, XS1403, XS1404</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S801 is currently wave3_planned with deferred_reason 'Wave 3 series — requires Ch8 cross-study comparison framework'. However, both required input series exist and are calculated: S506 (ST exploitation rate, wave 1) and ES1401 (Mohun exploitation rate, wave 1). The raw Mohun data is present at Inputs/ExternalSources/Mohun/mohun_exploitation_rates_1948_1989.csv covering 42 years. The comparison therefore does not require new data collection — it requires implementing the Ch8 table construction (loader L13, processor P15) to assemble Book Table 8.1 side-by-side layout. The 1964-1989 overlap period gives 26 annual comparison points. The 1948-1963 period can be populated with ST data only (Mohun does not cover it).</t>
+          <t>S801 is currently wave3_planned with deferred_reason 'Wave 3 series — requires Ch8 cross-study comparison framework'. However, both required input series exist and are calculated: S506 (ST exploitation rate, wave 1) and XS1401 (Mohun exploitation rate, wave 1). The raw Mohun data is present at Inputs/ExternalSources/Mohun/mohun_exploitation_rates_1948_1989.csv covering 42 years. The comparison therefore does not require new data collection — it requires implementing the Ch8 table construction (loader L13, processor P15) to assemble Book Table 8.1 side-by-side layout. The 1964-1989 overlap period gives 26 annual comparison points. The 1948-1963 period can be populated with ST data only (Mohun does not cover it).</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>S801 is a cross-study comparison table placing ST (1994) exploitation rates (S506) alongside Mohun (2005) exploitation rates (ES1401) for the overlapping 1964-1989 period. The systematic ratio of ST/Mohun averages 1.61 (ES1404), driven by ST's narrower definition of productive labor (Lp &lt; 0.5L vs. Mohun's broader boundary). All input data exists; Wave 3 implementation requires only the Ch8 table construction logic.</t>
+          <t>S801 is a cross-study comparison table placing ST (1994) exploitation rates (S506) alongside Mohun (2005) exploitation rates (XS1401) for the overlapping 1964-1989 period. The systematic ratio of ST/Mohun averages 1.61 (XS1404), driven by ST's narrower definition of productive labor (Lp &lt; 0.5L vs. Mohun's broader boundary). All input data exists; Wave 3 implementation requires only the Ch8 table construction logic.</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mohun data file covers 1948-1989 per task brief but ES1401 registry year_range is 1964-2001 — verify whether Mohun 1948-1963 data is available in the CSV</t>
+          <t>Mohun data file covers 1948-1989 per task brief but XS1401 registry year_range is 1964-2001 — verify whether Mohun 1948-1963 data is available in the CSV</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ES1401</t>
+          <t>XS1401</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ES1402</t>
+          <t>XS1402</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ES1403</t>
+          <t>XS1403</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ES1404</t>
+          <t>XS1404</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S801.xlsx
+++ b/extenbooks/S801.xlsx
@@ -1374,7 +1374,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>- **Original research**: `Technical/research/S801_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T801_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 (`D3_RMWND_quotes_ch7_etc`) — the backfill specifically flagged that the book has no Ch8</t>
+          <t>- **Original research**: `Technical/research/S801_research.json`, researcher `agent`, 2026-05-06; ported from `predecessor-build/research/T801_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 (`D3_RMWND_quotes_ch7_etc`) — the backfill specifically flagged that the book has no Ch8</t>
         </is>
       </c>
     </row>
